--- a/Data/04_Klima og ressursforvaltning/Karbonrike arealer/Inndata/2020-2025/telemark_nedbygd_arealstatistikk_2020-2025.xlsx
+++ b/Data/04_Klima og ressursforvaltning/Karbonrike arealer/Inndata/2020-2025/telemark_nedbygd_arealstatistikk_2020-2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://telemarkfylke-my.sharepoint.com/personal/even_sannes_riiser_telemarkfylke_no/Documents/Github/Telemark/Data/04_Klima og ressursforvaltning/Karbonrike arealer/Inndata/2020-2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{6B1F7BFB-C0E9-453D-9C85-1F37A5516441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ECE4BE99-D17B-4CE8-8CB3-BCC6B451489B}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{6B1F7BFB-C0E9-453D-9C85-1F37A5516441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFEB569E-373E-4463-B9A6-02BA1823712C}"/>
   <bookViews>
-    <workbookView xWindow="57495" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{2B882C9C-F63E-46FD-9ED4-FDE21AC768FA}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="38610" windowHeight="20880" xr2:uid="{2B882C9C-F63E-46FD-9ED4-FDE21AC768FA}"/>
   </bookViews>
   <sheets>
     <sheet name="telemark_nedbygd_arealstatistik" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Kommunenavn</t>
   </si>
@@ -105,6 +105,9 @@
   </si>
   <si>
     <t>Nedbygd karbonrikt areal totalt</t>
+  </si>
+  <si>
+    <t>Telemark</t>
   </si>
 </sst>
 </file>
@@ -647,6 +650,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -966,7 +973,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6360EF2F-63B1-4F36-96B0-B0941D7C29AA}">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
@@ -1337,21 +1344,37 @@
         <v>624</v>
       </c>
     </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="1">
+        <f>SUM(B2:B18)</f>
+        <v>141</v>
+      </c>
+      <c r="C19" s="1">
+        <f t="shared" ref="C19:F19" si="0">SUM(C2:C18)</f>
+        <v>105</v>
+      </c>
+      <c r="D19" s="1">
+        <f t="shared" si="0"/>
+        <v>10862</v>
+      </c>
+      <c r="E19" s="1">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="F19" s="1">
+        <f t="shared" si="0"/>
+        <v>11128</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100066452AED51C564E81244154F306F214" ma:contentTypeVersion="14" ma:contentTypeDescription="Opprett et nytt dokument." ma:contentTypeScope="" ma:versionID="f2a6e89e9fab0e1f3147bf49bc2f96bd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="aeab8c92-4fe2-4b74-b3c0-181f164372e7" xmlns:ns3="28a90a7f-539e-46e9-b8b5-332cc23d9dd7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3a626c1087cf45885e38492df0acdcc" ns2:_="" ns3:_="">
     <xsd:import namespace="aeab8c92-4fe2-4b74-b3c0-181f164372e7"/>
@@ -1564,6 +1587,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1576,14 +1608,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81AE2616-C3DC-4D2F-BCA2-4C7A577E6A44}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37EB8A1A-7675-4307-AFBE-2872ACC9C4D8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1598,6 +1622,14 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81AE2616-C3DC-4D2F-BCA2-4C7A577E6A44}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
